--- a/tables/TableS5.xlsx
+++ b/tables/TableS5.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS6_cross_population_replication" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS5_cross_population_replication" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -863,4 +864,35 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Supplementary Table S5. Cross-Population Replication Results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Summary of cross-population replication for RNH1 and key candidates across multiple datasets. Columns: Gene, Phenotype, Dataset (FinnGen R13, UKB GCST90043640, UKB Xue et al. 2022, Sakaue et al. 2021 DN), Z-score, P-value, Direction vs FinnGen eQTLGen, and Notes. Includes meta-analysis and heterogeneity metrics (Cochran Q=40.0, I²=95.0%, 95% PI [-4.00, +10.68]).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>